--- a/data/trans_orig/P33A-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P33A-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que las horas que duerme le permiten descansar lo suficiente en 2012</t>
+          <t>Población que las horas que duerme le permiten descansar lo suficiente en 2012 (tasa de respuesta: 99,23%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>810235</t>
+          <t>812742</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>855651</t>
+          <t>857712</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>83,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>926350</t>
+          <t>925294</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>994055</t>
+          <t>990000</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>69,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>74,78%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1754034</t>
+          <t>1753608</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1836127</t>
+          <t>1834413</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>76,33%</t>
+          <t>76,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>79,83%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>112947</t>
+          <t>110886</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>158363</t>
+          <t>155856</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>335302</t>
+          <t>339357</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>403007</t>
+          <t>404063</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>461828</t>
+          <t>463542</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>543921</t>
+          <t>544347</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,69%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1638004</t>
+          <t>1639726</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1699945</t>
+          <t>1699691</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>84,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1231928</t>
+          <t>1233678</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1310687</t>
+          <t>1307623</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>70,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2893517</t>
+          <t>2891445</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2994016</t>
+          <t>2994552</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>78,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>81,18%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>248292</t>
+          <t>248546</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>310233</t>
+          <t>308511</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>429996</t>
+          <t>433060</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>508755</t>
+          <t>507005</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>694904</t>
+          <t>694368</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>795403</t>
+          <t>797475</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,62%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>357623</t>
+          <t>357064</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>394623</t>
+          <t>393838</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>74,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>335185</t>
+          <t>335389</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>371172</t>
+          <t>371523</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>73,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>81,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>702227</t>
+          <t>704540</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>756068</t>
+          <t>755009</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>75,07%</t>
+          <t>75,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>80,82%</t>
+          <t>80,71%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>83183</t>
+          <t>83968</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>120183</t>
+          <t>120742</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>86483</t>
+          <t>86132</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>122470</t>
+          <t>122266</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>179393</t>
+          <t>180452</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>233234</t>
+          <t>230921</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>24,69%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2837488</t>
+          <t>2838823</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2925830</t>
+          <t>2925646</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2533111</t>
+          <t>2535614</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2638857</t>
+          <t>2641986</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>71,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>74,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5396024</t>
+          <t>5396714</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5535370</t>
+          <t>5536031</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>77,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>79,97%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>468810</t>
+          <t>468994</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>557152</t>
+          <t>555817</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>888838</t>
+          <t>885709</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>994584</t>
+          <t>992081</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1386966</t>
+          <t>1386305</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1526312</t>
+          <t>1525622</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,04%</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que las horas que duerme le permiten descansar lo suficiente en 2016</t>
+          <t>Población que las horas que duerme le permiten descansar lo suficiente en 2016 (tasa de respuesta: 98,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2335,12 +2335,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>609528</t>
+          <t>607497</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>648269</t>
+          <t>646494</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>81,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>675159</t>
+          <t>676859</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>734799</t>
+          <t>737175</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2385,12 +2385,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>69,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1299688</t>
+          <t>1297101</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1370441</t>
+          <t>1368716</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>75,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>79,61%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>96502</t>
+          <t>98277</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>135243</t>
+          <t>137274</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>239802</t>
+          <t>237426</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>299442</t>
+          <t>297742</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>348931</t>
+          <t>350656</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>419684</t>
+          <t>422271</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,56%</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1712034</t>
+          <t>1714254</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1780703</t>
+          <t>1778157</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>83,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1444658</t>
+          <t>1443480</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1524539</t>
+          <t>1524427</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>73,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3178476</t>
+          <t>3180485</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3281269</t>
+          <t>3281364</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>79,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>81,51%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>272731</t>
+          <t>275277</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>341400</t>
+          <t>339180</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>447983</t>
+          <t>448095</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>527864</t>
+          <t>529042</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>744686</t>
+          <t>744591</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>847479</t>
+          <t>845470</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,0%</t>
         </is>
       </c>
     </row>
@@ -3021,12 +3021,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>412690</t>
+          <t>414892</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>454920</t>
+          <t>455254</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>83,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>356976</t>
+          <t>355558</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>398977</t>
+          <t>399728</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>66,3%</t>
+          <t>66,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>74,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>783666</t>
+          <t>783225</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>840604</t>
+          <t>841036</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>72,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>77,79%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>87908</t>
+          <t>87574</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>130138</t>
+          <t>127936</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>139414</t>
+          <t>138663</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>181415</t>
+          <t>182833</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>240614</t>
+          <t>240182</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>297552</t>
+          <t>297993</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,56%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2765120</t>
+          <t>2763295</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2857837</t>
+          <t>2853057</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2515849</t>
+          <t>2513389</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2620982</t>
+          <t>2616289</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>72,18%</t>
+          <t>72,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>75,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5313388</t>
+          <t>5315215</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5447174</t>
+          <t>5455415</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>77,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>79,91%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>483195</t>
+          <t>487975</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>575912</t>
+          <t>577737</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>864532</t>
+          <t>869225</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>969665</t>
+          <t>972125</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1379371</t>
+          <t>1371130</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1513157</t>
+          <t>1511330</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,14%</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que las horas que duerme le permiten descansar lo suficiente en 2023</t>
+          <t>Población que las horas que duerme le permiten descansar lo suficiente en 2023 (tasa de respuesta: 99,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3938,12 +3938,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>355355</t>
+          <t>355295</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>391328</t>
+          <t>392868</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>69,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>453020</t>
+          <t>456986</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>492995</t>
+          <t>495825</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>821258</t>
+          <t>821865</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>875184</t>
+          <t>876862</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4023,12 +4023,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>65,11%</t>
+          <t>65,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,39%</t>
+          <t>69,52%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>122727</t>
+          <t>121187</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>158700</t>
+          <t>158760</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>254283</t>
+          <t>251453</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>294258</t>
+          <t>290292</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>386149</t>
+          <t>384471</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>440075</t>
+          <t>439468</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>34,84%</t>
         </is>
       </c>
     </row>
@@ -4281,12 +4281,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1915413</t>
+          <t>1914782</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2061639</t>
+          <t>2070235</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4296,12 +4296,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>84,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4316,12 +4316,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1708593</t>
+          <t>1708931</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1905696</t>
+          <t>1906526</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4331,12 +4331,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>76,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3650591</t>
+          <t>3650459</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3890523</t>
+          <t>3894343</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>86,5%</t>
         </is>
       </c>
     </row>
@@ -4394,12 +4394,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>216539</t>
+          <t>207943</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>362765</t>
+          <t>363396</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>318246</t>
+          <t>317416</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>515349</t>
+          <t>515011</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>611597</t>
+          <t>607777</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>851529</t>
+          <t>851661</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,92%</t>
         </is>
       </c>
     </row>
@@ -4624,12 +4624,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>496056</t>
+          <t>495287</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>549353</t>
+          <t>547680</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4659,12 +4659,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>496754</t>
+          <t>497144</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>533006</t>
+          <t>533670</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>75,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4694,12 +4694,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1011034</t>
+          <t>1010200</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1073071</t>
+          <t>1072387</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4709,12 +4709,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>77,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>82,64%</t>
         </is>
       </c>
     </row>
@@ -4737,12 +4737,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>93925</t>
+          <t>95598</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>147222</t>
+          <t>147991</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>121437</t>
+          <t>120773</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>157689</t>
+          <t>157299</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>224650</t>
+          <t>225334</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>286687</t>
+          <t>287521</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4822,12 +4822,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,16%</t>
         </is>
       </c>
     </row>
@@ -4967,12 +4967,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2807989</t>
+          <t>2809473</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2994478</t>
+          <t>3003177</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>81,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5002,12 +5002,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2693347</t>
+          <t>2697206</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2953939</t>
+          <t>2916416</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>74,29%</t>
+          <t>74,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5533245</t>
+          <t>5535864</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5819519</t>
+          <t>5830111</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5052,12 +5052,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,57%</t>
         </is>
       </c>
     </row>
@@ -5080,12 +5080,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>441033</t>
+          <t>432334</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>627522</t>
+          <t>626038</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5115,12 +5115,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>671724</t>
+          <t>709247</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>932316</t>
+          <t>928457</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1241655</t>
+          <t>1231063</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1527929</t>
+          <t>1525310</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5165,12 +5165,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,6%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P33A-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P33A-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>812742</t>
+          <t>812485</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>857712</t>
+          <t>855472</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>83,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>925294</t>
+          <t>928978</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>990000</t>
+          <t>995072</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>69,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>74,47%</t>
+          <t>74,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1753608</t>
+          <t>1754886</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1834413</t>
+          <t>1837036</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>76,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>79,94%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>110886</t>
+          <t>113126</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>155856</t>
+          <t>156113</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>339357</t>
+          <t>334285</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>404063</t>
+          <t>400379</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>463542</t>
+          <t>460919</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>544347</t>
+          <t>543069</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,63%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1639726</t>
+          <t>1639941</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1699691</t>
+          <t>1705019</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>84,16%</t>
+          <t>84,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>87,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1233678</t>
+          <t>1231832</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1307623</t>
+          <t>1308855</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>70,87%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>75,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2891445</t>
+          <t>2893129</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2994552</t>
+          <t>2991082</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>78,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>81,08%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>248546</t>
+          <t>243218</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>308511</t>
+          <t>308296</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>433060</t>
+          <t>431828</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>507005</t>
+          <t>508851</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>694368</t>
+          <t>697838</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>797475</t>
+          <t>795791</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,57%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>357064</t>
+          <t>358516</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>393838</t>
+          <t>396354</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>74,73%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>335389</t>
+          <t>332379</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>371523</t>
+          <t>369880</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>72,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>80,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>704540</t>
+          <t>702761</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>755009</t>
+          <t>755501</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>80,76%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>83968</t>
+          <t>81452</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>120742</t>
+          <t>119290</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>86132</t>
+          <t>87775</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>122266</t>
+          <t>125276</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>180452</t>
+          <t>179960</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>230921</t>
+          <t>232700</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,88%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2838823</t>
+          <t>2838482</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2925646</t>
+          <t>2925153</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2535614</t>
+          <t>2532200</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2641986</t>
+          <t>2642179</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>74,89%</t>
+          <t>74,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5396714</t>
+          <t>5399020</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5536031</t>
+          <t>5539138</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>77,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>80,02%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>468994</t>
+          <t>469487</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>555817</t>
+          <t>556158</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>885709</t>
+          <t>885516</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>992081</t>
+          <t>995495</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1386305</t>
+          <t>1383198</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1525622</t>
+          <t>1523316</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>22,01%</t>
         </is>
       </c>
     </row>
@@ -2335,12 +2335,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>607497</t>
+          <t>608600</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>646494</t>
+          <t>647133</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>86,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>676859</t>
+          <t>675204</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>737175</t>
+          <t>735366</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2385,12 +2385,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>69,45%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>75,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1297101</t>
+          <t>1299401</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1368716</t>
+          <t>1370014</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>75,44%</t>
+          <t>75,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>79,68%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>98277</t>
+          <t>97638</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>137274</t>
+          <t>136171</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>237426</t>
+          <t>239235</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>297742</t>
+          <t>299397</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>350656</t>
+          <t>349358</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>422271</t>
+          <t>419971</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,43%</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1714254</t>
+          <t>1711345</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1778157</t>
+          <t>1780162</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1443480</t>
+          <t>1446388</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1524427</t>
+          <t>1523582</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>73,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>77,28%</t>
+          <t>77,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3180485</t>
+          <t>3181778</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3281364</t>
+          <t>3284488</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>79,0%</t>
+          <t>79,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>81,58%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>275277</t>
+          <t>273272</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>339180</t>
+          <t>342089</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>448095</t>
+          <t>448940</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>529042</t>
+          <t>526134</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>744591</t>
+          <t>741467</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>845470</t>
+          <t>844177</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>20,97%</t>
         </is>
       </c>
     </row>
@@ -3021,12 +3021,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>414892</t>
+          <t>415746</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>455254</t>
+          <t>455184</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>76,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>355558</t>
+          <t>357375</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>399728</t>
+          <t>398173</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>66,04%</t>
+          <t>66,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>74,24%</t>
+          <t>73,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>783225</t>
+          <t>782557</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>841036</t>
+          <t>843052</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>72,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>77,97%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>87574</t>
+          <t>87644</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>127936</t>
+          <t>127082</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>138663</t>
+          <t>140218</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>182833</t>
+          <t>181016</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>240182</t>
+          <t>238166</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>297993</t>
+          <t>298661</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,62%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2763295</t>
+          <t>2770327</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2853057</t>
+          <t>2854652</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>82,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2513389</t>
+          <t>2515476</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2616289</t>
+          <t>2622168</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>75,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5315215</t>
+          <t>5304951</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5455415</t>
+          <t>5449991</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>77,86%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>79,84%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>487975</t>
+          <t>486380</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>577737</t>
+          <t>570705</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>869225</t>
+          <t>863346</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>972125</t>
+          <t>970038</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1371130</t>
+          <t>1376554</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1511330</t>
+          <t>1521594</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,29%</t>
         </is>
       </c>
     </row>
@@ -3933,32 +3933,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>374441</t>
+          <t>428492</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>355295</t>
+          <t>407844</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>392868</t>
+          <t>447668</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>74,19%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3968,32 +3968,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>474219</t>
+          <t>511541</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>456986</t>
+          <t>490332</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>495825</t>
+          <t>531806</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>63,46%</t>
+          <t>62,77%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>61,15%</t>
+          <t>60,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>66,35%</t>
+          <t>65,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4003,32 +4003,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>848660</t>
+          <t>940033</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>821865</t>
+          <t>910860</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>876862</t>
+          <t>972904</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>67,51%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>69,87%</t>
         </is>
       </c>
     </row>
@@ -4046,32 +4046,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>139614</t>
+          <t>149046</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>121187</t>
+          <t>129870</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>158760</t>
+          <t>169694</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4081,32 +4081,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>273059</t>
+          <t>303402</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>251453</t>
+          <t>283137</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>290292</t>
+          <t>324611</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>39,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4116,32 +4116,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>412673</t>
+          <t>452448</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>384471</t>
+          <t>419577</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>439468</t>
+          <t>481621</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>34,59%</t>
         </is>
       </c>
     </row>
@@ -4159,17 +4159,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514055</t>
+          <t>577538</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514055</t>
+          <t>577538</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514055</t>
+          <t>577538</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4194,17 +4194,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>747278</t>
+          <t>814943</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>747278</t>
+          <t>814943</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>747278</t>
+          <t>814943</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4229,17 +4229,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1261333</t>
+          <t>1392481</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1261333</t>
+          <t>1392481</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1261333</t>
+          <t>1392481</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4276,32 +4276,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1970003</t>
+          <t>1887818</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1914782</t>
+          <t>1851900</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2070235</t>
+          <t>1922235</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>85,1%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>83,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4311,32 +4311,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1777364</t>
+          <t>1649693</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1708931</t>
+          <t>1612216</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1906526</t>
+          <t>1682792</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>79,92%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>76,84%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>3747367</t>
+          <t>3537512</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3650459</t>
+          <t>3484639</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3894343</t>
+          <t>3585198</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>80,85%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>79,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>81,94%</t>
         </is>
       </c>
     </row>
@@ -4389,32 +4389,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>308175</t>
+          <t>330515</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>207943</t>
+          <t>296098</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>363396</t>
+          <t>366433</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4424,32 +4424,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>446578</t>
+          <t>507248</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>317416</t>
+          <t>474149</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>515011</t>
+          <t>544725</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4459,32 +4459,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>754753</t>
+          <t>837762</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>607777</t>
+          <t>790076</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>851661</t>
+          <t>890635</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>20,36%</t>
         </is>
       </c>
     </row>
@@ -4502,17 +4502,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2278178</t>
+          <t>2218333</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2278178</t>
+          <t>2218333</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2278178</t>
+          <t>2218333</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4537,17 +4537,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2223942</t>
+          <t>2156941</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2223942</t>
+          <t>2156941</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2223942</t>
+          <t>2156941</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4572,17 +4572,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4502120</t>
+          <t>4375274</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4502120</t>
+          <t>4375274</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4502120</t>
+          <t>4375274</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4619,32 +4619,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>526810</t>
+          <t>586902</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>495287</t>
+          <t>563443</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>547680</t>
+          <t>606640</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>82,91%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>79,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>85,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4654,32 +4654,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>516896</t>
+          <t>574757</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>497144</t>
+          <t>553977</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>533670</t>
+          <t>593528</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>78,86%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>76,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>81,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4689,32 +4689,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1043705</t>
+          <t>1161658</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1010200</t>
+          <t>1130963</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1072387</t>
+          <t>1195225</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>80,86%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>78,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>83,19%</t>
         </is>
       </c>
     </row>
@@ -4732,32 +4732,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>116468</t>
+          <t>121006</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>95598</t>
+          <t>101268</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>147991</t>
+          <t>144465</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4767,32 +4767,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>137547</t>
+          <t>154035</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>120773</t>
+          <t>135264</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>157299</t>
+          <t>174815</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4802,32 +4802,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>254016</t>
+          <t>275042</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>225334</t>
+          <t>241475</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>287521</t>
+          <t>305737</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>21,28%</t>
         </is>
       </c>
     </row>
@@ -4845,17 +4845,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>643278</t>
+          <t>707908</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>643278</t>
+          <t>707908</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>643278</t>
+          <t>707908</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4880,17 +4880,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>654443</t>
+          <t>728792</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>654443</t>
+          <t>728792</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>654443</t>
+          <t>728792</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4915,17 +4915,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1297721</t>
+          <t>1436700</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1297721</t>
+          <t>1436700</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1297721</t>
+          <t>1436700</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4962,32 +4962,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2871254</t>
+          <t>2903212</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2809473</t>
+          <t>2856513</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3003177</t>
+          <t>2948564</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4997,32 +4997,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2768479</t>
+          <t>2735991</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2697206</t>
+          <t>2690049</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2916416</t>
+          <t>2781870</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>73,93%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>74,39%</t>
+          <t>72,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>75,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5032,32 +5032,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>5639732</t>
+          <t>5639203</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5535864</t>
+          <t>5574367</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5830111</t>
+          <t>5706064</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>78,27%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>77,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>79,2%</t>
         </is>
       </c>
     </row>
@@ -5075,32 +5075,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>564257</t>
+          <t>600567</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>432334</t>
+          <t>555215</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>626038</t>
+          <t>647266</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5110,32 +5110,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>857184</t>
+          <t>964685</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>709247</t>
+          <t>918806</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>928457</t>
+          <t>1010627</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5145,32 +5145,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1421442</t>
+          <t>1565252</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1231063</t>
+          <t>1498391</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1525310</t>
+          <t>1630088</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>22,63%</t>
         </is>
       </c>
     </row>
@@ -5188,17 +5188,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3435511</t>
+          <t>3503779</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3435511</t>
+          <t>3503779</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3435511</t>
+          <t>3503779</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5223,17 +5223,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3625663</t>
+          <t>3700676</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3625663</t>
+          <t>3700676</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3625663</t>
+          <t>3700676</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5258,17 +5258,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7061174</t>
+          <t>7204455</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7061174</t>
+          <t>7204455</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7061174</t>
+          <t>7204455</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
